--- a/input/Zomorod_Supplier_Intelligence_180_AUTOFILL.xlsx
+++ b/input/Zomorod_Supplier_Intelligence_180_AUTOFILL.xlsx
@@ -6840,7 +6840,6 @@
           <t>dressing, bandage, foam dressing, hydrocolloid, silicone dressing, wound, plaster</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6853,7 +6852,6 @@
           <t>syringe, needle, hypodermic, luer lock, luer slip, insulin syringe, scalp vein</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6866,7 +6864,6 @@
           <t>iv cannula, cannula, venflon, iv catheter</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6879,7 +6876,6 @@
           <t>infusion set, iv set, drip set, transfusion set, burette</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6892,7 +6888,6 @@
           <t>foley, catheter, suction catheter, nelaton, urinary catheter, urology</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6905,7 +6900,6 @@
           <t>nitrile glove, latex glove, vinyl glove, examination glove, surgical glove</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6918,7 +6912,6 @@
           <t>mask, respirator, gown, coverall, face shield, cap, shoe cover</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6931,7 +6924,6 @@
           <t>gauze, gauze roll, gauze swab, bandage roll, crepe bandage, cotton</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6944,7 +6936,6 @@
           <t>alcohol swab, disinfectant, sanitizer, antiseptic, povidone, chlorhexidine</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6957,7 +6948,6 @@
           <t>vacutainer, tube, pipette, specimen, lancet, sample cup, centrifuge tube</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7230,7 +7220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7267,11 +7257,49 @@
           <t>2026-03-04T20:40:09.227035Z</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Workbook generated. Run scraper in Codespaces to populate Supplier_Intelligence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-04T21:07:25.402851Z</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Seed_URLs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Visited 0 seeds; wrote 0 email-verified rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-04T21:08:01.918741Z</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Seed_URLs</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Visited 0 seeds; wrote 0 email-verified rows.</t>
         </is>
       </c>
     </row>
